--- a/diseases/d198/2026-2029.xlsx
+++ b/diseases/d198/2026-2029.xlsx
@@ -769,11 +769,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4143982721811539</v>
+        <v>0.4131422153939487</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BR-AC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Acre, Brazil</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -899,29 +899,26 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>249</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1165934121730026</v>
+        <v>2.027497369885356</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -950,42 +947,7389 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BR-AL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alagoas, Brazil</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5277654287566343</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BR-AM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amazonas, Brazil</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>37</v>
+      </c>
+      <c r="O5" t="n">
+        <v>37</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8484436562326442</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BR-AP</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Amapá, Brazil</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BR-BA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bahia, Brazil</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>78</v>
+      </c>
+      <c r="O7" t="n">
+        <v>78</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5238600804649084</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BR-CE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ceará, Brazil</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>28</v>
+      </c>
+      <c r="O8" t="n">
+        <v>28</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3010037076131685</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2657810840944639</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BR-ES</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Espírito Santo, Brazil</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.04818473642467328</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BR-GO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goiás, Brazil</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>31</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4136072516291789</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BR-MA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Maranhão, Brazil</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>32</v>
+      </c>
+      <c r="O12" t="n">
+        <v>32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4555447411132118</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Minas Gerais, Brazil</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>68</v>
+      </c>
+      <c r="O13" t="n">
+        <v>68</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3168640007127576</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1357627166391125</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BR-MT</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mato Grosso, Brazil</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>21</v>
+      </c>
+      <c r="O15" t="n">
+        <v>21</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5316011573716626</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BR-PA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pará, Brazil</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>45</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5139142864060307</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BR-PB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paraíba, Brazil</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>23</v>
+      </c>
+      <c r="O17" t="n">
+        <v>23</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5498672190202417</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pernambuco, Brazil</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>43</v>
+      </c>
+      <c r="O18" t="n">
+        <v>43</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4487030187069506</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BR-PI</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Piauí, Brazil</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2947577047453338</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>BR-PR</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paraná, Brazil</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>53</v>
+      </c>
+      <c r="O20" t="n">
+        <v>53</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4434235106157262</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>BR-RJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>45</v>
+      </c>
+      <c r="O21" t="n">
+        <v>45</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2612419675351704</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BR-RN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte, Brazil</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>26</v>
+      </c>
+      <c r="O22" t="n">
+        <v>26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.7506343582090673</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>BR-RO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rondônia, Brazil</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>22</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.251893488901964</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BR-RR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Roraima, Brazil</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>85</v>
+      </c>
+      <c r="O25" t="n">
+        <v>85</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.756677658077307</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Santa Catarina, Brazil</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>39</v>
+      </c>
+      <c r="O26" t="n">
+        <v>39</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.4691583143454538</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BR-SE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sergipe, Brazil</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>12</v>
+      </c>
+      <c r="O27" t="n">
+        <v>12</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.5200985586768693</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>117</v>
+      </c>
+      <c r="O28" t="n">
+        <v>117</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2533618738626867</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>BR-TO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tocantins, Brazil</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>21</v>
+      </c>
+      <c r="O29" t="n">
+        <v>21</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.315794420279776</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>249</v>
+      </c>
+      <c r="O30" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.1162400131447381</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AW30" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BA30" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BB30" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BC30" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BR-AC</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Acre, Brazil</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.337916228314226</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BR-AL</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alagoas, Brazil</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.09313507566293547</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BR-AM</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Amazonas, Brazil</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1146545481395465</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BR-AP</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Amapá, Brazil</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>BR-BA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bahia, Brazil</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>13</v>
+      </c>
+      <c r="O35" t="n">
+        <v>13</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.08731001341081807</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BR-CE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ceará, Brazil</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>12</v>
+      </c>
+      <c r="O36" t="n">
+        <v>12</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.1290015889770722</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BR-DF</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Distrito Federal, Brazil</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.132890542047232</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BR-ES</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Espírito Santo, Brazil</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BR-GO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goiás, Brazil</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>13</v>
+      </c>
+      <c r="O39" t="n">
+        <v>13</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.1734482022961073</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>BR-MA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Maranhão, Brazil</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>11</v>
+      </c>
+      <c r="O40" t="n">
+        <v>11</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.1565935047576666</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Minas Gerais, Brazil</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>18</v>
+      </c>
+      <c r="O41" t="n">
+        <v>18</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.08387576489455348</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BR-MT</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Mato Grosso, Brazil</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.1265717041361102</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BR-PA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pará, Brazil</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>17</v>
+      </c>
+      <c r="O44" t="n">
+        <v>17</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.1941453970867227</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BR-PB</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Paraíba, Brazil</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>7</v>
+      </c>
+      <c r="O45" t="n">
+        <v>7</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.167350892745291</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pernambuco, Brazil</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>10</v>
+      </c>
+      <c r="O46" t="n">
+        <v>10</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.1043495392341746</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BR-PI</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Piauí, Brazil</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BR-PR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Paraná, Brazil</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>31</v>
+      </c>
+      <c r="O48" t="n">
+        <v>31</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.2593609213035379</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BR-RJ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.03483226233802272</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BR-RN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte, Brazil</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>11</v>
+      </c>
+      <c r="O50" t="n">
+        <v>11</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.3175760746269131</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BR-RO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rondônia, Brazil</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.2845212474777191</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BR-RR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Roraima, Brazil</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>22</v>
+      </c>
+      <c r="O53" t="n">
+        <v>22</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.1958459820905971</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Santa Catarina, Brazil</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>21</v>
+      </c>
+      <c r="O54" t="n">
+        <v>21</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.2526237077244751</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BR-SE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sergipe, Brazil</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>5</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.2167077327820289</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>20</v>
+      </c>
+      <c r="O56" t="n">
+        <v>20</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.04330972202780969</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>toxoplasmosis-in-pregnancy</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BR-TO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tocantins, Brazil</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D198</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis in pregnancy</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>妊娠期弓形虫病</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.4385981400932585</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1105,7 +8449,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -1115,7 +8459,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1167,7 +8511,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1134</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d198/2026-2029.xlsx
+++ b/diseases/d198/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1193,6 +1208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1329,6 +1349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1465,6 +1490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1601,6 +1631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1737,6 +1772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1873,6 +1913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2009,6 +2054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2145,6 +2195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2281,6 +2336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2417,6 +2477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2553,6 +2618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2689,6 +2759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2825,6 +2900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2961,6 +3041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3097,6 +3182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3233,6 +3323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3369,6 +3464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3505,6 +3605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3641,6 +3746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3913,6 +4028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4049,6 +4169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4185,6 +4310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4321,6 +4451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4457,6 +4592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4596,6 +4736,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4741,6 +4886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4877,6 +5027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5013,6 +5168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5149,6 +5309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5285,6 +5450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5421,6 +5591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5557,6 +5732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5693,6 +5873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5829,6 +6014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5965,6 +6155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6101,6 +6296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6237,6 +6437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6373,6 +6578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6509,6 +6719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6645,6 +6860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6781,6 +7001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6917,6 +7142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7053,6 +7283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7189,6 +7424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7325,6 +7565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7461,6 +7706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7733,6 +7988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7869,6 +8129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8005,6 +8270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8141,6 +8411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8275,6 +8550,11 @@
       <c r="S57" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">

--- a/diseases/d198/2026-2029.xlsx
+++ b/diseases/d198/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.4131422153939487</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>2.027497369885356</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1062,11 +1032,6 @@
       <c r="R4" t="n">
         <v>0.5277654287566343</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1079,22 +1044,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1203,11 +1158,6 @@
       <c r="R5" t="n">
         <v>0.8484436562326442</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1220,22 +1170,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1344,11 +1284,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1361,22 +1296,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1485,11 +1410,6 @@
       <c r="R7" t="n">
         <v>0.5238600804649084</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1502,22 +1422,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1626,11 +1536,6 @@
       <c r="R8" t="n">
         <v>0.3010037076131685</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1643,22 +1548,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1767,11 +1662,6 @@
       <c r="R9" t="n">
         <v>0.2657810840944639</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1784,22 +1674,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1908,11 +1788,6 @@
       <c r="R10" t="n">
         <v>0.04818473642467328</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1925,22 +1800,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2049,11 +1914,6 @@
       <c r="R11" t="n">
         <v>0.4136072516291789</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2066,22 +1926,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2190,11 +2040,6 @@
       <c r="R12" t="n">
         <v>0.4555447411132118</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2207,22 +2052,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2331,11 +2166,6 @@
       <c r="R13" t="n">
         <v>0.3168640007127576</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2348,22 +2178,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2472,11 +2292,6 @@
       <c r="R14" t="n">
         <v>0.1357627166391125</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2489,22 +2304,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2613,11 +2418,6 @@
       <c r="R15" t="n">
         <v>0.5316011573716626</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2630,22 +2430,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2754,11 +2544,6 @@
       <c r="R16" t="n">
         <v>0.5139142864060307</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2771,22 +2556,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2895,11 +2670,6 @@
       <c r="R17" t="n">
         <v>0.5498672190202417</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2912,22 +2682,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3036,11 +2796,6 @@
       <c r="R18" t="n">
         <v>0.4487030187069506</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3053,22 +2808,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3177,11 +2922,6 @@
       <c r="R19" t="n">
         <v>0.2947577047453338</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3194,22 +2934,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3318,11 +3048,6 @@
       <c r="R20" t="n">
         <v>0.4434235106157262</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3060,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3459,11 +3174,6 @@
       <c r="R21" t="n">
         <v>0.2612419675351704</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3476,22 +3186,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3600,11 +3300,6 @@
       <c r="R22" t="n">
         <v>0.7506343582090673</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3617,22 +3312,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3741,11 +3426,6 @@
       <c r="R23" t="n">
         <v>1.251893488901964</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3758,22 +3438,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3882,11 +3552,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3899,22 +3564,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4023,11 +3678,6 @@
       <c r="R25" t="n">
         <v>0.756677658077307</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4040,22 +3690,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4164,11 +3804,6 @@
       <c r="R26" t="n">
         <v>0.4691583143454538</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4181,22 +3816,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4305,11 +3930,6 @@
       <c r="R27" t="n">
         <v>0.5200985586768693</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4322,22 +3942,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4446,11 +4056,6 @@
       <c r="R28" t="n">
         <v>0.2533618738626867</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4463,22 +4068,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4587,11 +4182,6 @@
       <c r="R29" t="n">
         <v>1.315794420279776</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4604,22 +4194,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4731,11 +4311,6 @@
       <c r="R30" t="n">
         <v>0.1162400131447381</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4748,22 +4323,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4881,11 +4446,6 @@
       <c r="R31" t="n">
         <v>0.337916228314226</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4898,22 +4458,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5022,11 +4572,6 @@
       <c r="R32" t="n">
         <v>0.09313507566293547</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5039,22 +4584,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5163,11 +4698,6 @@
       <c r="R33" t="n">
         <v>0.1146545481395465</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5180,22 +4710,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5304,11 +4824,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5321,22 +4836,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5445,11 +4950,6 @@
       <c r="R35" t="n">
         <v>0.08731001341081807</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5462,22 +4962,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5586,11 +5076,6 @@
       <c r="R36" t="n">
         <v>0.1290015889770722</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5603,22 +5088,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5727,11 +5202,6 @@
       <c r="R37" t="n">
         <v>0.132890542047232</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5744,22 +5214,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5868,11 +5328,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5885,22 +5340,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6009,11 +5454,6 @@
       <c r="R39" t="n">
         <v>0.1734482022961073</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6026,22 +5466,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6150,11 +5580,6 @@
       <c r="R40" t="n">
         <v>0.1565935047576666</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6167,22 +5592,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6291,11 +5706,6 @@
       <c r="R41" t="n">
         <v>0.08387576489455348</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6308,22 +5718,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6432,11 +5832,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5844,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6573,11 +5958,6 @@
       <c r="R43" t="n">
         <v>0.1265717041361102</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6590,22 +5970,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6714,11 +6084,6 @@
       <c r="R44" t="n">
         <v>0.1941453970867227</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6731,22 +6096,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6855,11 +6210,6 @@
       <c r="R45" t="n">
         <v>0.167350892745291</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6872,22 +6222,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6996,11 +6336,6 @@
       <c r="R46" t="n">
         <v>0.1043495392341746</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7013,22 +6348,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7137,11 +6462,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7154,22 +6474,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7278,11 +6588,6 @@
       <c r="R48" t="n">
         <v>0.2593609213035379</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7295,22 +6600,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7419,11 +6714,6 @@
       <c r="R49" t="n">
         <v>0.03483226233802272</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7436,22 +6726,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7560,11 +6840,6 @@
       <c r="R50" t="n">
         <v>0.3175760746269131</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7577,22 +6852,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7701,11 +6966,6 @@
       <c r="R51" t="n">
         <v>0.2845212474777191</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7718,22 +6978,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7842,11 +7092,6 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7859,22 +7104,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7983,11 +7218,6 @@
       <c r="R53" t="n">
         <v>0.1958459820905971</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8000,22 +7230,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8124,11 +7344,6 @@
       <c r="R54" t="n">
         <v>0.2526237077244751</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8141,22 +7356,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8265,11 +7470,6 @@
       <c r="R55" t="n">
         <v>0.2167077327820289</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8282,22 +7482,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8406,11 +7596,6 @@
       <c r="R56" t="n">
         <v>0.04330972202780969</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8423,22 +7608,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8547,11 +7722,6 @@
       <c r="R57" t="n">
         <v>0.4385981400932585</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8564,22 +7734,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>

--- a/diseases/d198/2026-2029.xlsx
+++ b/diseases/d198/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0.4131422153939487</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,13 +788,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>2.027497369885356</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,13 +938,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -935,6 +965,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>web</t>
@@ -950,7 +985,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC3" t="inlineStr">
         <is>
           <t>web</t>
@@ -1032,6 +1071,11 @@
       <c r="R4" t="n">
         <v>0.5277654287566343</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1044,13 +1088,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1061,6 +1115,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>web</t>
@@ -1076,7 +1135,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
@@ -1158,6 +1221,11 @@
       <c r="R5" t="n">
         <v>0.8484436562326442</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1170,13 +1238,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1187,6 +1265,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>web</t>
@@ -1202,7 +1285,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC5" t="inlineStr">
         <is>
           <t>web</t>
@@ -1284,6 +1371,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1296,13 +1388,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1313,6 +1415,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>web</t>
@@ -1328,7 +1435,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
@@ -1410,6 +1521,11 @@
       <c r="R7" t="n">
         <v>0.5238600804649084</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1422,13 +1538,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1439,6 +1565,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>web</t>
@@ -1454,7 +1585,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC7" t="inlineStr">
         <is>
           <t>web</t>
@@ -1536,6 +1671,11 @@
       <c r="R8" t="n">
         <v>0.3010037076131685</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1548,13 +1688,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1565,6 +1715,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>web</t>
@@ -1580,7 +1735,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC8" t="inlineStr">
         <is>
           <t>web</t>
@@ -1662,6 +1821,11 @@
       <c r="R9" t="n">
         <v>0.2657810840944639</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1674,13 +1838,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1691,6 +1865,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>web</t>
@@ -1706,7 +1885,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC9" t="inlineStr">
         <is>
           <t>web</t>
@@ -1788,6 +1971,11 @@
       <c r="R10" t="n">
         <v>0.04818473642467328</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1800,13 +1988,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -1817,6 +2015,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>web</t>
@@ -1832,7 +2035,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC10" t="inlineStr">
         <is>
           <t>web</t>
@@ -1914,6 +2121,11 @@
       <c r="R11" t="n">
         <v>0.4136072516291789</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1926,13 +2138,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -1943,6 +2165,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>web</t>
@@ -1958,7 +2185,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC11" t="inlineStr">
         <is>
           <t>web</t>
@@ -2040,6 +2271,11 @@
       <c r="R12" t="n">
         <v>0.4555447411132118</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2052,13 +2288,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2069,6 +2315,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2084,7 +2335,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC12" t="inlineStr">
         <is>
           <t>web</t>
@@ -2166,6 +2421,11 @@
       <c r="R13" t="n">
         <v>0.3168640007127576</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2178,13 +2438,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2195,6 +2465,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2210,7 +2485,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
@@ -2292,6 +2571,11 @@
       <c r="R14" t="n">
         <v>0.1357627166391125</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2304,13 +2588,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2321,6 +2615,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2336,7 +2635,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC14" t="inlineStr">
         <is>
           <t>web</t>
@@ -2418,6 +2721,11 @@
       <c r="R15" t="n">
         <v>0.5316011573716626</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2430,13 +2738,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2447,6 +2765,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2462,7 +2785,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC15" t="inlineStr">
         <is>
           <t>web</t>
@@ -2544,6 +2871,11 @@
       <c r="R16" t="n">
         <v>0.5139142864060307</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2556,13 +2888,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2573,6 +2915,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2588,7 +2935,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC16" t="inlineStr">
         <is>
           <t>web</t>
@@ -2670,6 +3021,11 @@
       <c r="R17" t="n">
         <v>0.5498672190202417</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2682,13 +3038,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -2699,6 +3065,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2714,7 +3085,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC17" t="inlineStr">
         <is>
           <t>web</t>
@@ -2796,6 +3171,11 @@
       <c r="R18" t="n">
         <v>0.4487030187069506</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2808,13 +3188,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -2825,6 +3215,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2840,7 +3235,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC18" t="inlineStr">
         <is>
           <t>web</t>
@@ -2922,6 +3321,11 @@
       <c r="R19" t="n">
         <v>0.2947577047453338</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2934,13 +3338,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -2951,6 +3365,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>web</t>
@@ -2966,7 +3385,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC19" t="inlineStr">
         <is>
           <t>web</t>
@@ -3048,6 +3471,11 @@
       <c r="R20" t="n">
         <v>0.4434235106157262</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3060,13 +3488,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3077,6 +3515,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3092,7 +3535,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC20" t="inlineStr">
         <is>
           <t>web</t>
@@ -3174,6 +3621,11 @@
       <c r="R21" t="n">
         <v>0.2612419675351704</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3186,13 +3638,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3203,6 +3665,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3218,7 +3685,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC21" t="inlineStr">
         <is>
           <t>web</t>
@@ -3300,6 +3771,11 @@
       <c r="R22" t="n">
         <v>0.7506343582090673</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3312,13 +3788,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3329,6 +3815,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3344,7 +3835,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC22" t="inlineStr">
         <is>
           <t>web</t>
@@ -3426,6 +3921,11 @@
       <c r="R23" t="n">
         <v>1.251893488901964</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3438,13 +3938,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3455,6 +3965,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3470,7 +3985,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC23" t="inlineStr">
         <is>
           <t>web</t>
@@ -3552,6 +4071,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3564,13 +4088,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -3581,6 +4115,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3596,7 +4135,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC24" t="inlineStr">
         <is>
           <t>web</t>
@@ -3678,6 +4221,11 @@
       <c r="R25" t="n">
         <v>0.756677658077307</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3690,13 +4238,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -3707,6 +4265,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3722,7 +4285,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC25" t="inlineStr">
         <is>
           <t>web</t>
@@ -3804,6 +4371,11 @@
       <c r="R26" t="n">
         <v>0.4691583143454538</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3816,13 +4388,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -3833,6 +4415,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3848,7 +4435,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC26" t="inlineStr">
         <is>
           <t>web</t>
@@ -3930,6 +4521,11 @@
       <c r="R27" t="n">
         <v>0.5200985586768693</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3942,13 +4538,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -3959,6 +4565,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>web</t>
@@ -3974,7 +4585,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC27" t="inlineStr">
         <is>
           <t>web</t>
@@ -4056,6 +4671,11 @@
       <c r="R28" t="n">
         <v>0.2533618738626867</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4068,13 +4688,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4085,6 +4715,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4100,7 +4735,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC28" t="inlineStr">
         <is>
           <t>web</t>
@@ -4182,6 +4821,11 @@
       <c r="R29" t="n">
         <v>1.315794420279776</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4194,13 +4838,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4211,6 +4865,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4226,7 +4885,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC29" t="inlineStr">
         <is>
           <t>web</t>
@@ -4311,6 +4974,11 @@
       <c r="R30" t="n">
         <v>0.1162400131447381</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4323,13 +4991,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -4446,6 +5124,11 @@
       <c r="R31" t="n">
         <v>0.337916228314226</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4458,13 +5141,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -4475,6 +5168,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>web</t>
@@ -4490,7 +5188,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC31" t="inlineStr">
         <is>
           <t>web</t>
@@ -4572,6 +5274,11 @@
       <c r="R32" t="n">
         <v>0.09313507566293547</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4584,13 +5291,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -4601,6 +5318,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4616,7 +5338,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC32" t="inlineStr">
         <is>
           <t>web</t>
@@ -4698,6 +5424,11 @@
       <c r="R33" t="n">
         <v>0.1146545481395465</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4710,13 +5441,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -4727,6 +5468,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4742,7 +5488,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC33" t="inlineStr">
         <is>
           <t>web</t>
@@ -4824,6 +5574,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4836,13 +5591,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -4853,6 +5618,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4868,7 +5638,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC34" t="inlineStr">
         <is>
           <t>web</t>
@@ -4950,6 +5724,11 @@
       <c r="R35" t="n">
         <v>0.08731001341081807</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4962,13 +5741,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -4979,6 +5768,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>web</t>
@@ -4994,7 +5788,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC35" t="inlineStr">
         <is>
           <t>web</t>
@@ -5076,6 +5874,11 @@
       <c r="R36" t="n">
         <v>0.1290015889770722</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5088,13 +5891,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5105,6 +5918,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5120,7 +5938,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC36" t="inlineStr">
         <is>
           <t>web</t>
@@ -5202,6 +6024,11 @@
       <c r="R37" t="n">
         <v>0.132890542047232</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5214,13 +6041,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5231,6 +6068,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5246,7 +6088,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC37" t="inlineStr">
         <is>
           <t>web</t>
@@ -5328,6 +6174,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5340,13 +6191,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5357,6 +6218,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5372,7 +6238,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC38" t="inlineStr">
         <is>
           <t>web</t>
@@ -5454,6 +6324,11 @@
       <c r="R39" t="n">
         <v>0.1734482022961073</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5466,13 +6341,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -5483,6 +6368,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5498,7 +6388,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC39" t="inlineStr">
         <is>
           <t>web</t>
@@ -5580,6 +6474,11 @@
       <c r="R40" t="n">
         <v>0.1565935047576666</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5592,13 +6491,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -5609,6 +6518,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5624,7 +6538,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC40" t="inlineStr">
         <is>
           <t>web</t>
@@ -5706,6 +6624,11 @@
       <c r="R41" t="n">
         <v>0.08387576489455348</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5718,13 +6641,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -5735,6 +6668,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5750,7 +6688,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC41" t="inlineStr">
         <is>
           <t>web</t>
@@ -5832,6 +6774,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5844,13 +6791,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -5861,6 +6818,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>web</t>
@@ -5876,7 +6838,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC42" t="inlineStr">
         <is>
           <t>web</t>
@@ -5958,6 +6924,11 @@
       <c r="R43" t="n">
         <v>0.1265717041361102</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5970,13 +6941,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -5987,6 +6968,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>web</t>
@@ -6002,7 +6988,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC43" t="inlineStr">
         <is>
           <t>web</t>
@@ -6084,6 +7074,11 @@
       <c r="R44" t="n">
         <v>0.1941453970867227</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6096,13 +7091,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6113,6 +7118,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>web</t>
@@ -6128,7 +7138,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC44" t="inlineStr">
         <is>
           <t>web</t>
@@ -6210,6 +7224,11 @@
       <c r="R45" t="n">
         <v>0.167350892745291</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6222,13 +7241,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6239,6 +7268,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>web</t>
@@ -6254,7 +7288,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC45" t="inlineStr">
         <is>
           <t>web</t>
@@ -6336,6 +7374,11 @@
       <c r="R46" t="n">
         <v>0.1043495392341746</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6348,13 +7391,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -6365,6 +7418,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>web</t>
@@ -6380,7 +7438,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC46" t="inlineStr">
         <is>
           <t>web</t>
@@ -6462,6 +7524,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6474,13 +7541,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -6491,6 +7568,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>web</t>
@@ -6506,7 +7588,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC47" t="inlineStr">
         <is>
           <t>web</t>
@@ -6588,6 +7674,11 @@
       <c r="R48" t="n">
         <v>0.2593609213035379</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6600,13 +7691,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -6617,6 +7718,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>web</t>
@@ -6632,7 +7738,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC48" t="inlineStr">
         <is>
           <t>web</t>
@@ -6714,6 +7824,11 @@
       <c r="R49" t="n">
         <v>0.03483226233802272</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6726,13 +7841,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -6743,6 +7868,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>web</t>
@@ -6758,7 +7888,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC49" t="inlineStr">
         <is>
           <t>web</t>
@@ -6840,6 +7974,11 @@
       <c r="R50" t="n">
         <v>0.3175760746269131</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6852,13 +7991,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -6869,6 +8018,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>web</t>
@@ -6884,7 +8038,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC50" t="inlineStr">
         <is>
           <t>web</t>
@@ -6966,6 +8124,11 @@
       <c r="R51" t="n">
         <v>0.2845212474777191</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6978,13 +8141,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -6995,6 +8168,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>web</t>
@@ -7010,7 +8188,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC51" t="inlineStr">
         <is>
           <t>web</t>
@@ -7092,6 +8274,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7104,13 +8291,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7121,6 +8318,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>web</t>
@@ -7136,7 +8338,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC52" t="inlineStr">
         <is>
           <t>web</t>
@@ -7218,6 +8424,11 @@
       <c r="R53" t="n">
         <v>0.1958459820905971</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7230,13 +8441,23 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -7247,6 +8468,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>web</t>
@@ -7262,7 +8488,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC53" t="inlineStr">
         <is>
           <t>web</t>
@@ -7344,6 +8574,11 @@
       <c r="R54" t="n">
         <v>0.2526237077244751</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7356,13 +8591,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -7373,6 +8618,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7388,7 +8638,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7470,6 +8724,11 @@
       <c r="R55" t="n">
         <v>0.2167077327820289</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7482,13 +8741,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -7499,6 +8768,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>web</t>
@@ -7514,7 +8788,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
@@ -7596,6 +8874,11 @@
       <c r="R56" t="n">
         <v>0.04330972202780969</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7608,13 +8891,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -7625,6 +8918,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>web</t>
@@ -7640,7 +8938,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC56" t="inlineStr">
         <is>
           <t>web</t>
@@ -7722,6 +9024,11 @@
       <c r="R57" t="n">
         <v>0.4385981400932585</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7734,13 +9041,23 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -7751,6 +9068,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>web</t>
@@ -7766,7 +9088,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB57" t="inlineStr"/>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC57" t="inlineStr">
         <is>
           <t>web</t>
